--- a/lessons/qr/excels/remarks_lcs.xlsx
+++ b/lessons/qr/excels/remarks_lcs.xlsx
@@ -787,7 +787,7 @@
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">

--- a/lessons/qr/excels/remarks_lcs.xlsx
+++ b/lessons/qr/excels/remarks_lcs.xlsx
@@ -58,11 +58,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1551,24 +1554,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1589,24 +1574,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1659,7 +1626,6 @@
           <t>+&gt; (00:00:00), +&gt; (00:00:00), +ID (00:00:00), +cplumn (00:00:00), +f80 (00:00:00), +mapmarker (00:00:00), +positioning (00:00:00), +positioning (00:00:00), -Positioning (12:19:41.715), -&gt; (12:21:30.386), -Positioning (12:21:32.906), -column (12:27:17.320), -id (12:31:25.626), -280 (12:41:14.808), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -mapContainer (12:50:07.768), -function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -&gt; (12:59:50.485), -let (13:00:39.047), -scannerOn (13:00:41.475), -= (13:00:41.932), -false (13:00:43.302), -; (13:00:43.381), -function (13:01:58.048), -toggleScanner (13:02:00.332), -( (13:02:00.435), -) (13:02:00.635), -{ (13:02:00.822), -} (13:02:01.916), -scannerOn (13:02:03.160), -= (13:02:03.504), -! (13:02:03.955), -scannerOn (13:02:05.438), -; (13:02:05.679), -if (13:02:24.440), -( (13:02:24.770), -scannerOn (13:02:26.202), -) (13:02:26.386), -{ (13:02:26.756), -} (13:02:27.642), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -startScanner (13:11:29.686), -( (13:11:29.781), -) (13:11:30.046), -; (13:11:30.413), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -function (13:12:04.020), -startScanner (13:12:06.965), -( (13:12:07.303), -) (13:12:07.652), -{ (13:12:08.465), -} (13:12:17.001), -reader (13:12:18.420), -. (13:12:18.578), -start (13:12:21.297), -( (13:12:21.528), -) (13:12:35.212), -{ (13:12:35.257), -facingMode (13:12:37.968), -: (13:12:38.283), -" (13:12:38.976), -environment (13:12:42.232), -" (13:12:42.606), -} (13:13:14.032), -, (13:13:15.191), -{ (13:13:21.432), -} (13:13:21.856), -, (13:13:22.080), -function (13:13:33.410), -( (13:13:33.790), -text (13:13:34.463), -) (13:13:34.671), -{ (13:13:35.039), -} (13:13:55.224), -. (13:14:34.576), -catch (13:14:36.086), -( (13:14:36.285), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>92.3</v>
       </c>
@@ -1684,12 +1650,11 @@
           <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -let (13:00:39.047), -scannerOn (13:00:41.475), -= (13:00:41.932), -false (13:00:43.302), -; (13:00:43.381), -function (13:01:58.048), -toggleScanner (13:02:00.332), -( (13:02:00.435), -) (13:02:00.635), -{ (13:02:00.822), -} (13:02:01.916), -scannerOn (13:02:03.160), -= (13:02:03.504), -! (13:02:03.955), -scannerOn (13:02:05.438), -; (13:02:05.679), -if (13:02:24.440), -( (13:02:24.770), -scannerOn (13:02:26.202), -) (13:02:26.386), -{ (13:02:26.756), -} (13:02:27.642), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -startScanner (13:11:29.686), -( (13:11:29.781), -) (13:11:30.046), -; (13:11:30.413), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -function (13:12:04.020), -startScanner (13:12:06.965), -( (13:12:07.303), -) (13:12:07.652), -{ (13:12:08.465), -} (13:12:17.001), -reader (13:12:18.420), -. (13:12:18.578), -start (13:12:21.297), -( (13:12:21.528), -) (13:12:35.212), -{ (13:12:35.257), -facingMode (13:12:37.968), -: (13:12:38.283), -" (13:12:38.976), -environment (13:12:42.232), -" (13:12:42.606), -} (13:13:14.032), -, (13:13:15.191), -{ (13:13:21.432), -} (13:13:21.856), -, (13:13:22.080), -function (13:13:33.410), -( (13:13:33.790), -text (13:13:34.463), -) (13:13:34.671), -{ (13:13:35.039), -} (13:13:55.224), -. (13:14:34.576), -catch (13:14:36.086), -( (13:14:36.285), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1706,22 +1671,6 @@
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1738,22 +1687,6 @@
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1769,24 +1702,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1807,24 +1722,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1846,22 +1743,6 @@
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1877,24 +1758,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1915,24 +1778,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -1985,7 +1830,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +% (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +SCRIPT (00:00:00), +SCRIPT (00:00:00), +SRC (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -script (13:05:47.673), -src (13:05:48.559), -script (13:06:51.081), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>97.3</v>
       </c>
@@ -2010,12 +1854,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2031,24 +1874,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2101,7 +1926,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +654321 (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +btn (00:00:00), +btn (00:00:00), +cancel (00:00:00), +div (00:00:00), +facingmode (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +mapcontainer (00:00:00), +mapcontainer (00:00:00), +market (00:00:00), +scan (00:00:00), +showMarKerAt (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), -123456 (12:24:02.680), -marker (12:35:44.425), -&gt; (12:35:45.158), -&lt; (12:49:02.019), -/ (12:49:02.029), -div (12:49:02.059), -&gt; (12:49:02.069), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -function (12:56:10.245), -showMarkerAt (12:56:12.525), -&lt; (12:59:27.700), -button (12:59:28.610), -id (12:59:29.226), -= (12:59:29.495), -" (12:59:30.073), -" (12:59:30.083), -btn (12:59:30.502), -onclick (12:59:42.303), -= (12:59:42.561), -" (12:59:43.422), -" (12:59:43.432), -toggleScanner (12:59:48.978), -( (12:59:49.262), -) (12:59:49.819), -&gt; (12:59:50.485), -&lt; (13:00:19.793), -/ (13:00:19.803), -button (13:00:19.863), -&gt; (13:00:19.873), -SCAN (13:00:21.378), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -&lt; (13:05:46.381), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -&gt; (13:07:18.033), -facingMode (13:12:37.968), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>60.5</v>
       </c>
@@ -2113,7 +1937,6 @@
       <c r="O14" t="n">
         <v>100</v>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="n">
         <v>70.2</v>
       </c>
@@ -2122,12 +1945,11 @@
           <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -facingMode (13:12:37.968), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -showMarkerAt (13:20:05.930), -toggleScanner (13:20:36.733), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapcontainer (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +cancel (00:00:00), +" (00:00:00), +; (00:00:00), +mapcontainer (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +facingmode (00:00:00), +showMarKerAt (00:00:00), +togglescanner (00:00:00), +showMarKerAt (00:00:00)</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2143,24 +1965,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2181,24 +1985,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2219,24 +2005,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2257,24 +2025,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2327,7 +2077,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +Btn (00:00:00), +CANCEL (00:00:00), +Document (00:00:00), +Positionaning (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +camere (00:00:00), +console (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -QR (12:19:38.447), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -" (12:29:12.696), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -map (12:31:27.486), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -function (12:56:10.245), -btn (12:59:30.502), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -camera (13:10:05.606), -; (13:11:40.424), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
         <v>81.40000000000001</v>
       </c>
@@ -2352,12 +2101,11 @@
           <t>-function (12:56:10.245), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -camera (13:10:05.606), -; (13:11:40.424), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), +camere (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +console (00:00:00), +. (00:00:00)</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2373,24 +2121,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2472,12 +2202,11 @@
           <t>-marker (12:56:29.330), -marker (12:57:07.602), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Cancel (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Scan (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00)</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2493,24 +2222,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2531,24 +2242,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2630,12 +2323,11 @@
           <t>-btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2683,7 +2375,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +123456 (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +H1 (00:00:00), +H1 (00:00:00), +btn (00:00:00), +btn (00:00:00), +cancel (00:00:00), +console (00:00:00), +h1 (00:00:00), +h1 (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +js (00:00:00), +log (00:00:00), +mapcontainer (00:00:00), +mapcontainer (00:00:00), +positioning (00:00:00), +positioning (00:00:00), +scan (00:00:00), +scan (00:00:00), +script (00:00:00), +script (00:00:00), +src (00:00:00), +text (00:00:00), -&lt; (12:19:35.874), -Positioning (12:19:41.715), -h1 (12:21:29.653), -h1 (12:21:30.376), -Positioning (12:21:32.906), -" (12:29:12.696), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -map (12:31:27.486), -mapContainer (12:49:01.909), -mapContainer (12:50:07.768), -&lt; (12:52:43.997), -script (12:52:45.286), -src (12:52:46.196), -= (12:52:46.360), -" (12:52:47.087), -" (12:52:47.097), -123456 (12:52:48.540), -. (12:52:48.877), -js (12:52:49.268), -&gt; (12:53:03.064), -&lt; (12:53:08.112), -/ (12:53:08.122), -script (12:53:08.182), -&gt; (12:53:08.192), -SCAN (13:00:21.378), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -script (13:05:47.673), -src (13:05:48.559), -= (13:05:48.773), -" (13:05:49.475), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -/ (13:05:50.743), -/ (13:05:50.962), -unpkg (13:05:51.928), -. (13:05:52.210), -com (13:05:52.875), -/ (13:05:52.996), -html5 (13:05:54.075), -- (13:05:54.209), -qrcode (13:05:55.667), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -&gt; (13:06:05.501), -&lt; (13:06:51.011), -/ (13:06:51.021), -script (13:06:51.081), -&gt; (13:06:51.091), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
         <v>62.7</v>
       </c>
@@ -2708,12 +2399,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +cancel (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +console (00:00:00), +. (00:00:00), +log (00:00:00), +( (00:00:00), +text (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2729,24 +2419,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2767,24 +2439,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2806,22 +2460,6 @@
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2837,24 +2475,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -2894,7 +2514,6 @@
       <c r="H30" t="n">
         <v>100</v>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>93.90000000000001</v>
       </c>
@@ -2903,7 +2522,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +sqrcode (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -qrcode (13:05:55.667), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>99.09999999999999</v>
       </c>
@@ -2915,7 +2533,6 @@
       <c r="O30" t="n">
         <v>100</v>
       </c>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
         <v>83</v>
       </c>
@@ -2924,12 +2541,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3006,12 +2622,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3027,24 +2642,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3065,24 +2662,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3103,24 +2682,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3141,24 +2702,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3211,7 +2754,6 @@
           <t>+" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), += (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +innerText (00:00:00), +positioning (00:00:00), +positioning (00:00:00), +showMarketAt (00:00:00), +startsScanner (00:00:00), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -: (13:05:50.571), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997)</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>93.2</v>
       </c>
@@ -3223,7 +2765,6 @@
       <c r="O36" t="n">
         <v>100</v>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
         <v>83.5</v>
       </c>
@@ -3232,12 +2773,11 @@
           <t>-; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +" (00:00:00), +; (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S36" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3253,24 +2793,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3291,24 +2813,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3329,24 +2833,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3367,24 +2853,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3437,7 +2905,6 @@
           <t>+&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +Container (00:00:00), +http (00:00:00), +innertext (00:00:00), +item (00:00:00), +map (00:00:00), +market (00:00:00), +market (00:00:00), +readerv (00:00:00), +scan (00:00:00), +scan (00:00:00), +srcipt (00:00:00), +srcipt (00:00:00), +sript (00:00:00), +sript (00:00:00), +startscanner8 (00:00:00), -&lt; (12:19:34.294), -&lt; (12:19:35.624), -&lt; (12:21:30.346), -items (12:27:20.468), -} (12:27:40.523), -marker (12:35:44.425), -marker (12:36:09.957), -; (12:38:00.710), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -mapContainer (12:49:01.909), -&gt; (12:49:01.929), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -script (12:52:45.286), -script (12:53:08.182), -function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -SCAN (13:00:21.378), -} (13:02:27.642), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -script (13:05:47.673), -https (13:05:50.422), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -" (13:05:57.902), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -script (13:06:51.081), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>85.5</v>
       </c>
@@ -3462,12 +2929,6 @@
           <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -( (12:56:12.784), -top (12:56:19.284), -, (12:56:19.472), -left (12:56:20.617), -) (12:56:24.879), -{ (12:56:25.450), -} (12:56:27.578), -marker (12:56:29.330), -. (12:56:32.992), -style (12:56:34.700), -. (12:56:34.846), -top (12:56:35.686), -= (12:56:36.236), -top (12:56:37.105), -; (12:56:37.291), -marker (12:57:07.602), -. (12:57:08.218), -style (12:57:17.355), -. (12:57:17.643), -left (12:57:18.355), -= (12:57:18.822), -left (12:57:19.699), -; (12:57:19.987), -} (13:02:27.642), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -else (13:02:35.145), -{ (13:02:35.627), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -reader (13:09:44.738), -startScanner (13:11:29.686), -stopScanner (13:11:39.450), -( (13:11:39.694), -) (13:11:40.064), -; (13:11:40.424), -} (13:12:17.001), -function (13:14:37.982), -( (13:14:38.459), -err (13:14:39.062), -) (13:14:39.334), -{ (13:14:39.786), -} (13:14:52.011), -) (13:14:52.021), -; (13:14:52.031), -console (13:14:53.426), -. (13:14:53.521), -error (13:14:54.485), -( (13:14:54.646), -err (13:14:55.390), -) (13:14:55.605), -; (13:14:55.882), -function (13:15:07.592), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -. (13:19:54.258), -parse (13:19:55.262), -( (13:19:55.567), -text (13:19:56.801), -) (13:19:56.883), -; (13:19:57.418), -showMarkerAt (13:20:05.930), -( (13:20:06.018), -place (13:20:07.207), -. (13:20:07.365), -top (13:20:08.076), -, (13:20:08.279), -place (13:20:09.533), -. (13:20:09.648), -left (13:20:10.640), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -) (13:20:37.437), -; (13:20:37.714), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +readerv (00:00:00), +startscanner8 (00:00:00), +innertext (00:00:00), +scan (00:00:00)</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>_</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3515,7 +2976,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +Artial (00:00:00), +Border (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +SCAn (00:00:00), +btn (00:00:00), +btn (00:00:00), +http (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +market (00:00:00), +positioning (00:00:00), +showMarketAt (00:00:00), +srcipt (00:00:00), -Positioning (12:19:41.715), -Arial (12:27:44.328), -marker (12:36:09.957), -border (12:38:55.775), -; (12:42:02.654), -script (12:52:45.286), -SCAN (13:00:21.378), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -https (13:05:50.422), -; (13:11:40.424), -showMarkerAt (13:20:05.930)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>96.40000000000001</v>
       </c>
@@ -3540,12 +3000,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -showMarkerAt (13:20:05.930), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S42" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3561,24 +3020,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3599,24 +3040,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3669,7 +3092,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +envitonment (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +mapContainner (00:00:00), +mapContainner (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -; (13:08:30.584), -environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
         <v>99.09999999999999</v>
       </c>
@@ -3694,12 +3116,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -environment (13:12:42.232), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), +mapContainner (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +mapContainner (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +envitonment (00:00:00)</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3747,7 +3168,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +( (00:00:00), +) (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +BigInt (00:00:00), +CANCEl (00:00:00), +Marker (00:00:00), +Marker (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +div (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +onClick (00:00:00), +positioning (00:00:00), -Positioning (12:19:41.715), -marker (12:56:29.330), -marker (12:57:07.602), -onclick (12:59:42.303), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
         <v>96.40000000000001</v>
       </c>
@@ -3772,12 +3192,11 @@
           <t>-marker (12:56:29.330), -marker (12:57:07.602), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +( (00:00:00), +) (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEl (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +Marker (00:00:00), +Marker (00:00:00)</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S46" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3794,22 +3213,6 @@
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3857,7 +3260,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +? (00:00:00), +CANCLE (00:00:00), +OR (00:00:00), +OR (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +enviroment (00:00:00), +green (00:00:00), +herf (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +lime (00:00:00), +scannerON (00:00:00), +showMarketAt (00:00:00), +strat (00:00:00), +sytlesheet (00:00:00), +togglescanner (00:00:00), +veiwport (00:00:00), -! (12:19:34.144), -viewport (12:19:34.954), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -/ (12:19:35.634), -title (12:19:35.684), -&gt; (12:19:35.694), -QR (12:19:38.447), -/ (12:21:30.356), -QR (12:21:30.856), -stylesheet (12:23:47.522), -href (12:23:59.034), -# (12:41:14.043), -280 (12:41:14.808), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -toggleScanner (12:59:48.978), -scannerOn (13:00:41.475), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -&gt; (13:06:51.091), -; (13:11:40.424), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>88.2</v>
       </c>
@@ -3882,12 +3284,11 @@
           <t>-scannerOn (13:00:41.475), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -start (13:12:21.297), -environment (13:12:42.232), -showMarkerAt (13:20:05.930), +scannerON (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCLE (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +" (00:00:00), +; (00:00:00), +strat (00:00:00), +enviroment (00:00:00), +showMarketAt (00:00:00), +? (00:00:00)</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S48" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3903,24 +3304,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -3973,7 +3356,6 @@
           <t>+# (00:00:00), +- (00:00:00), +280 (00:00:00), +; (00:00:00), +PNG (00:00:00), +red (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00), +viewpoint (00:00:00), -viewport (12:19:34.954), -png (12:30:36.357), -} (12:32:35.009), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -; (12:35:35.609), -# (12:36:08.726), -marker (12:36:09.957), -{ (12:36:10.360), -width (12:36:18.827), -: (12:36:19.115), -3vw (12:36:23.573), -; (12:36:25.789), -height (12:37:16.574), -: (12:37:16.693), -3vw (12:37:18.454), -; (12:37:19.456), -black (12:37:31.976), -; (12:37:32.154), -border (12:37:58.210), -- (12:37:58.480), -radius (12:37:59.488), -: (12:37:59.684), -50 (12:38:00.274), -% (12:38:00.472), -; (12:38:00.710), -outline (12:38:33.154), -: (12:38:33.436), -5px (12:38:34.274), -solid (12:38:36.469), -border (12:38:55.775), -: (12:38:55.983), -5px (12:38:56.840), -solid (12:38:57.986), -white (12:38:59.153), -; (12:38:59.359), -: (12:40:53.960), -root (12:40:54.816), -{ (12:41:00.473), -} (12:41:02.034), -- (12:41:02.747), -- (12:41:03.057), -theme (12:41:04.838), -: (12:41:13.006), -# (12:41:14.043), -280 (12:41:14.808), -; (12:41:15.160), -var (12:41:59.152), -( (12:41:59.354), -- (12:42:00.189), -- (12:42:00.527), -theme (12:42:01.928), -) (12:42:02.226), -var (12:42:26.709), -( (12:42:27.101), -- (12:42:28.230), -- (12:42:28.548), -theme (12:42:29.855), -) (12:42:30.228), -; (12:42:31.537), -position (12:44:00.909), -: (12:44:01.045), -absolute (12:44:03.220), -; (12:44:03.644), -top (12:44:05.651), -: (12:44:05.880), -0 (12:44:06.443), -; (12:44:06.772), -left (12:44:08.033), -: (12:44:08.227), -0 (12:44:08.691), -; (12:44:08.978), -transform (12:45:33.046), -: (12:45:33.314), -translate (12:45:34.855), -( (12:45:35.069), -- (12:45:35.321), -50 (12:45:35.855), -% (12:45:36.123), -, (12:45:36.383), -- (12:45:36.755), -50 (12:45:37.279), -% (12:45:37.687), -) (12:45:37.895), -# (12:50:05.962), -mapContainer (12:50:07.768), -{ (12:50:08.106), -} (12:50:08.969), -position (12:50:09.914), -: (12:50:10.045), -relative (12:50:11.261), -; (12:50:11.491), -showMarkerAt (12:56:12.525), -= (12:57:18.822), -" (13:02:39.256), -; (13:02:39.352), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -, (13:13:22.080), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
         <v>98.2</v>
       </c>
@@ -3998,12 +3380,11 @@
           <t>-showMarkerAt (12:56:12.525), -= (12:57:18.822), -" (13:02:39.256), -; (13:02:39.352), -, (13:13:22.080), -showMarkerAt (13:20:05.930), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -" (13:23:57.954), -; (13:23:57.997), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), +; (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00), +- (00:00:00)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4038,7 +3419,6 @@
       <c r="H51" t="n">
         <v>100</v>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>92.7</v>
       </c>
@@ -4047,7 +3427,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +apply (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +onClick (00:00:00), -/ (12:24:11.601), -onclick (12:59:42.303), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -4072,12 +3451,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +. (00:00:00), +apply (00:00:00)</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S51" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4093,24 +3471,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4131,24 +3491,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4169,24 +3511,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4207,24 +3531,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4277,15 +3583,12 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +Scan (00:00:00), +Stop (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>100</v>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>100</v>
       </c>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="n">
         <v>83</v>
       </c>
@@ -4294,12 +3597,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Stop (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +Scan (00:00:00)</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4315,24 +3617,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4353,24 +3637,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4423,7 +3689,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +console (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +log (00:00:00), +positioning (00:00:00), +startcanner (00:00:00), +} (00:00:00), -Positioning (12:19:41.715), -/ (12:24:11.601), -; (12:42:02.654), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -# (13:08:25.754), -camera (13:08:26.947), -{ (13:08:27.300), -} (13:08:28.277), -width (13:08:29.279), -: (13:08:29.526), -100 (13:08:30.270), -% (13:08:30.490), -; (13:08:30.584), -startScanner (13:11:29.686), -; (13:11:30.413), -; (13:11:40.424), -} (13:12:17.001), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>98.59999999999999</v>
       </c>
@@ -4448,12 +3713,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -startScanner (13:11:29.686), -; (13:11:30.413), -; (13:11:40.424), -} (13:12:17.001), -const (13:19:51.277), -place (13:19:52.497), -= (13:19:53.002), -JSON (13:19:54.041), -parse (13:19:55.262), -) (13:20:10.810), -; (13:20:11.131), -toggleScanner (13:20:36.733), -( (13:20:36.996), +startcanner (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +console (00:00:00), +log (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S59" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4469,24 +3733,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4539,7 +3785,6 @@
           <t>+) (00:00:00), +- (00:00:00), +- (00:00:00), +0 (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +: (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&gt; (00:00:00), +BigInt (00:00:00), +BigInt (00:00:00), +Facingmode (00:00:00), +OR (00:00:00), +OR (00:00:00), +ReadableStream (00:00:00), +align (00:00:00), +body (00:00:00), +body (00:00:00), +cancel (00:00:00), +center (00:00:00), +column (00:00:00), +direction (00:00:00), +display (00:00:00), +flex (00:00:00), +flex (00:00:00), +innertext (00:00:00), +innertext (00:00:00), +items (00:00:00), +mapcontainer (00:00:00), +margin (00:00:00), +positioning (00:00:00), +positioning (00:00:00), +scan (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +showMarkeAT (00:00:00), +{ (00:00:00), +} (00:00:00), -&gt; (12:19:35.694), -QR (12:19:38.447), -Positioning (12:19:41.715), -&gt; (12:21:30.386), -QR (12:21:30.856), -Positioning (12:21:32.906), -&lt; (12:23:38.378), -link (12:23:39.280), -rel (12:23:45.117), -= (12:23:45.277), -" (12:23:45.703), -" (12:23:45.713), -stylesheet (12:23:47.522), -href (12:23:59.034), -= (12:23:59.297), -" (12:24:00.025), -" (12:24:00.035), -123456 (12:24:02.680), -. (12:24:02.918), -css (12:24:03.855), -/ (12:24:11.601), -&lt; (12:49:01.709), -div (12:49:01.739), -id (12:49:01.769), -= (12:49:01.779), -" (12:49:01.789), -mapContainer (12:49:01.909), -" (12:49:01.919), -mapContainer (12:50:07.768), -; (12:50:11.491), -" (12:52:47.097), -function (12:56:10.245), -showMarkerAt (12:56:12.525), -&lt; (12:59:27.700), -&gt; (13:00:19.873), -scannerOn (13:00:41.475), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -) (13:12:35.212), -facingMode (13:12:37.968), -; (13:14:52.031), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402)</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>78.2</v>
       </c>
@@ -4564,12 +3809,11 @@
           <t>-function (12:56:10.245), -showMarkerAt (12:56:12.525), -scannerOn (13:00:41.475), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -innerText (13:02:29.574), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -{ (13:02:35.627), -} (13:02:36.228), -btn (13:02:36.869), -innerText (13:02:38.115), -SCAN (13:02:39.170), -const (13:09:43.272), -reader (13:09:44.738), -= (13:09:45.150), -new (13:09:46.009), -Html5Qrcode (13:09:48.612), -( (13:09:48.775), -" (13:09:49.070), -camera (13:10:05.606), -" (13:10:05.900), -) (13:10:06.349), -; (13:10:06.746), -reader (13:12:18.420), -) (13:12:35.212), -facingMode (13:12:37.968), -; (13:14:52.031), -stopScanner (13:15:09.792), -( (13:15:09.977), -) (13:15:10.190), -{ (13:15:10.634), -} (13:15:11.907), -reader (13:15:13.121), -. (13:15:13.234), -stop (13:15:14.065), -( (13:15:14.311), -) (13:15:14.407), -; (13:15:14.860), -, (13:20:08.279), -place (13:20:09.533), -; (13:20:11.131), -mapContainer (13:23:54.427), -. (13:23:54.581), -style (13:23:55.401), -. (13:23:55.474), -display (13:23:56.460), -= (13:23:56.827), -" (13:23:57.165), -none (13:23:57.811), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +cancel (00:00:00), +BigInt (00:00:00), +innertext (00:00:00), +scan (00:00:00), +ReadableStream (00:00:00), +Facingmode (00:00:00), +) (00:00:00), +showMarkeAT (00:00:00)</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S61" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4617,15 +3861,12 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +stopSCanner (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -stopScanner (13:15:09.792)</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
         <v>100</v>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
         <v>100</v>
       </c>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="n">
         <v>81.90000000000001</v>
       </c>
@@ -4634,12 +3875,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -stopScanner (13:15:09.792), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +stopSCanner (00:00:00)</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S62" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4655,24 +3895,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4693,24 +3915,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4731,24 +3935,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4770,22 +3956,6 @@
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4801,24 +3971,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4871,7 +4023,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +. (00:00:00), +/ (00:00:00), +/ (00:00:00), +123456 (00:00:00), +; (00:00:00), +; (00:00:00), +; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), +&lt; (00:00:00), += (00:00:00), += (00:00:00), += (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +&gt; (00:00:00), +BigInt (00:00:00), +BigInt (00:00:00), +black (00:00:00), +cancle (00:00:00), +div (00:00:00), +html15 (00:00:00), +http (00:00:00), +innertext (00:00:00), +innertext (00:00:00), +js (00:00:00), +mapcantainer (00:00:00), +mapcontainer (00:00:00), +mapcontainer (00:00:00), +positioning (00:00:00), +positioning (00:00:00), +scan (00:00:00), +scan (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +script (00:00:00), +script (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +src (00:00:00), +startscanner (00:00:00), +stopscanner (00:00:00), +togglescanner (00:00:00), +togglescanner (00:00:00), +togglescanner (00:00:00), +} (00:00:00), -Positioning (12:19:41.715), -Positioning (12:21:32.906), -/ (12:29:22.840), -; (12:41:15.160), -; (12:42:02.654), -mapContainer (12:49:01.909), -marker (12:56:29.330), -marker (12:57:07.602), -toggleScanner (12:59:48.978), -SCAN (13:00:21.378), -scannerOn (13:00:41.475), -toggleScanner (13:02:00.332), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -" (13:05:49.485), -https (13:05:50.422), -: (13:05:50.571), -html5 (13:05:54.075), -type (13:05:57.063), -= (13:05:57.290), -" (13:05:57.892), -text (13:06:02.121), -/ (13:06:02.343), -javascript (13:06:04.645), -; (13:08:30.584), -startScanner (13:12:06.965), -} (13:12:17.001), -; (13:14:52.031), -stopScanner (13:15:09.792), -toggleScanner (13:20:36.733), -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
         <v>80.90000000000001</v>
       </c>
@@ -4896,12 +4047,11 @@
           <t>-marker (12:56:29.330), -marker (12:57:07.602), -scannerOn (13:00:41.475), -toggleScanner (13:02:00.332), -scannerOn (13:02:03.160), -scannerOn (13:02:05.438), -scannerOn (13:02:26.202), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:02:39.352), -startScanner (13:12:06.965), -} (13:12:17.001), -; (13:14:52.031), -stopScanner (13:15:09.792), -toggleScanner (13:20:36.733), -; (13:20:37.714), -mapContainer (13:23:54.427), -mapContainer (13:24:12.088), -block (13:24:16.075), +scanneron (00:00:00), +togglescanner (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +scanneron (00:00:00), +mapcantainer (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innertext (00:00:00), += (00:00:00), +" (00:00:00), +cancle (00:00:00), +" (00:00:00), +; (00:00:00), +mapcontainer (00:00:00), +black (00:00:00), +" (00:00:00), +; (00:00:00), +BigInt (00:00:00), +. (00:00:00), +innertext (00:00:00), += (00:00:00), +" (00:00:00), +scan (00:00:00), +startscanner (00:00:00), +togglescanner (00:00:00), +stopscanner (00:00:00), +showMarkerAt (00:00:00), +showMarkerAt (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S68" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4917,24 +4067,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -4987,7 +4119,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +StartScanner (00:00:00), +btn (00:00:00), +btn (00:00:00), +html15 (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +positioning (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00), +startsScanner (00:00:00), -! (12:19:34.144), -- (12:19:35.194), -width (12:19:35.244), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -&gt; (12:19:35.454), -Positioning (12:19:41.715), -% (12:32:37.735), -margin (12:35:35.569), -: (12:35:35.579), -0 (12:35:35.599), -; (12:35:35.609), -showMarkerAt (12:56:12.525), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -html5 (13:05:54.075), -; (13:08:30.584), -startScanner (13:11:29.686), -; (13:11:30.413), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>93.59999999999999</v>
       </c>
@@ -5012,12 +4143,11 @@
           <t>-showMarkerAt (12:56:12.525), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -startScanner (13:11:29.686), -; (13:11:30.413), -; (13:11:40.424), -startScanner (13:12:06.965), -showMarkerAt (13:20:05.930), +StartScanner (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +" (00:00:00), +; (00:00:00), +startsScanner (00:00:00), +showMarketAt (00:00:00), +showMarketAt (00:00:00)</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S70" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5065,15 +4195,12 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>100</v>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
         <v>100</v>
       </c>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
         <v>83</v>
       </c>
@@ -5082,12 +4209,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S71" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5135,7 +4261,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +HTML5QRcode (00:00:00), +SCAN (00:00:00), +bnt (00:00:00), +bnt (00:00:00), +green (00:00:00), +html15 (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +maker (00:00:00), +maker (00:00:00), +maker (00:00:00), +maker (00:00:00), +showmarkerAt (00:00:00), +toggScanner (00:00:00), +top (00:00:00), -- (12:19:35.344), -scale (12:19:35.394), -= (12:19:35.404), -1 (12:19:35.414), -. (12:19:35.424), -0 (12:19:35.434), -" (12:19:35.444), -&gt; (12:19:35.454), -; (12:32:37.955), -marker (12:35:44.425), -marker (12:36:09.957), -# (12:41:14.043), -280 (12:41:14.808), -marker (12:56:29.330), -marker (12:57:07.602), -left (12:57:18.355), -toggleScanner (12:59:48.978), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -html5 (13:05:54.075), -Html5Qrcode (13:09:48.612), -; (13:11:40.424), -showMarkerAt (13:20:05.930)</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
         <v>93.59999999999999</v>
       </c>
@@ -5160,12 +4285,11 @@
           <t>-marker (12:56:29.330), -marker (12:57:07.602), -left (12:57:18.355), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -Html5Qrcode (13:09:48.612), -; (13:11:40.424), -showMarkerAt (13:20:05.930), +HTML5QRcode (00:00:00), +bnt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +bnt (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +showmarkerAt (00:00:00), +maker (00:00:00), +maker (00:00:00), +top (00:00:00)</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S72" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5213,11 +4337,9 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +HTML5Qrcode (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -; (12:42:02.654), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -Html5Qrcode (13:09:48.612), -; (13:11:40.424), -display (13:24:49.125), -: (13:24:49.342), -none (13:24:50.402), -; (13:24:50.519)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
         <v>100</v>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
         <v>96.7</v>
       </c>
@@ -5234,12 +4356,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -Html5Qrcode (13:09:48.612), -; (13:11:40.424), +HTML5Qrcode (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S73" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5255,24 +4376,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5294,22 +4397,6 @@
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5325,24 +4412,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5363,24 +4432,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5420,7 +4471,6 @@
       <c r="H78" t="n">
         <v>100</v>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>92.8</v>
       </c>
@@ -5429,7 +4479,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +onClick (00:00:00), +toogleScanner (00:00:00), -- (12:37:29.578), -color (12:37:30.642), -onclick (12:59:42.303), -toggleScanner (12:59:48.978), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
         <v>97.3</v>
       </c>
@@ -5454,12 +4503,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S78" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5507,15 +4555,12 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), +log (00:00:00), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -error (13:14:54.485)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
         <v>100</v>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
         <v>100</v>
       </c>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="n">
         <v>81.90000000000001</v>
       </c>
@@ -5524,12 +4569,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), -error (13:14:54.485), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00), +log (00:00:00)</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5545,24 +4589,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5615,11 +4641,9 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +SCAN (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -" (12:27:43.407), -" (12:27:44.570), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
         <v>100</v>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
         <v>98.7</v>
       </c>
@@ -5636,12 +4660,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S81" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5689,7 +4712,6 @@
           <t>+" (00:00:00), +" (00:00:00), +" (00:00:00), +" (00:00:00), +. (00:00:00), +. (00:00:00), +3vh (00:00:00), +; (00:00:00), +; (00:00:00), += (00:00:00), += (00:00:00), +CANCEL (00:00:00), +Postitioning (00:00:00), +SCAN (00:00:00), +Scan (00:00:00), +btn (00:00:00), +btn (00:00:00), +innerText (00:00:00), +innerText (00:00:00), -Positioning (12:21:32.906), -/ (12:24:11.601), -/ (12:29:22.840), -3vw (12:37:18.454), -SCAN (13:00:21.378), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424)</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
         <v>97.3</v>
       </c>
@@ -5714,12 +4736,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -btn (13:02:36.869), -. (13:02:36.966), -innerText (13:02:38.115), -= (13:02:38.418), -" (13:02:38.612), -SCAN (13:02:39.170), -" (13:02:39.256), -; (13:11:40.424), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCEL (00:00:00), +" (00:00:00), +; (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +SCAN (00:00:00)</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S82" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5767,7 +4788,6 @@
           <t>+" (00:00:00), +" (00:00:00), +. (00:00:00), +/ (00:00:00), +; (00:00:00), +&lt; (00:00:00), += (00:00:00), +&gt; (00:00:00), +CANCLE (00:00:00), +Html5QRcode (00:00:00), +SCANS (00:00:00), +btn (00:00:00), +head (00:00:00), +innerText (00:00:00), -&lt; (12:19:35.714), -/ (12:19:35.724), -head (12:19:35.764), -&gt; (12:24:11.796), -" (12:29:12.696), -id (12:31:25.626), -= (12:31:25.856), -" (12:31:26.515), -map (12:31:27.486), -% (12:45:36.123), -&gt; (13:00:19.873), -btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -SCAN (13:02:39.170), -; (13:02:39.352), -&lt; (13:07:13.849), -div (13:07:14.412), -id (13:07:14.951), -= (13:07:15.110), -" (13:07:15.683), -" (13:07:15.693), -camera (13:07:16.922), -&gt; (13:07:17.454), -&lt; (13:07:17.983), -/ (13:07:17.993), -div (13:07:18.023), -Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
         <v>88.59999999999999</v>
       </c>
@@ -5792,12 +4812,11 @@
           <t>-btn (13:02:28.137), -. (13:02:28.369), -innerText (13:02:29.574), -= (13:02:30.040), -" (13:02:30.222), -CANCEL (13:02:31.086), -" (13:02:31.386), -; (13:02:33.763), -SCAN (13:02:39.170), -; (13:02:39.352), -Html5Qrcode (13:09:48.612), -mapContainer (13:24:12.088), -. (13:24:12.217), -style (13:24:13.004), -. (13:24:13.132), -display (13:24:14.221), -= (13:24:14.902), -" (13:24:15.331), -block (13:24:16.075), -" (13:24:16.178), -; (13:24:16.460), +Html5QRcode (00:00:00), +" (00:00:00), +; (00:00:00), +btn (00:00:00), +. (00:00:00), +innerText (00:00:00), += (00:00:00), +" (00:00:00), +CANCLE (00:00:00), +SCANS (00:00:00)</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5813,24 +4832,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5851,24 +4852,6 @@
           <t>123456</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr">
         <is>
           <t>EXCLUDED</t>
@@ -5890,22 +4873,6 @@
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
       <c r="V86" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5927,22 +4894,6 @@
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -5964,22 +4915,6 @@
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6001,22 +4936,6 @@
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6038,22 +4957,6 @@
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
       <c r="V90" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6075,22 +4978,6 @@
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6112,22 +4999,6 @@
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6149,22 +5020,6 @@
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6186,22 +5041,6 @@
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6223,22 +5062,6 @@
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6260,22 +5083,6 @@
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6297,22 +5104,6 @@
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6334,22 +5125,6 @@
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6371,22 +5146,6 @@
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
           <t>LLM</t>
@@ -6408,22 +5167,6 @@
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
           <t>LLM</t>
